--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEVADA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEVADA_2019.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C298">
@@ -11623,7 +11623,7 @@
         <v>150</v>
       </c>
       <c r="D626">
-        <v>0.009056877188745321</v>
+        <v>0.009056877188745319</v>
       </c>
     </row>
     <row r="627">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C830">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C882">
